--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_251_R26.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_251_R26.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3216</v>
+        <v>6.4033</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1664</v>
+        <v>6.6513</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1553</v>
+        <v>-0.248</v>
       </c>
       <c r="G2" t="n">
         <v>1.1427</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2485</v>
+        <v>0.3301</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6765</v>
+        <v>0.1614</v>
       </c>
       <c r="U2" t="n">
-        <v>0.572</v>
+        <v>0.1687</v>
       </c>
       <c r="V2" t="n">
         <v>3.0748</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>S. LEE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3489</v>
+        <v>4.2649</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4294</v>
+        <v>3.3047</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9194</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4004</v>
+        <v>3.3554</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6349</v>
+        <v>0.2771</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2345</v>
+        <v>3.0783</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3949</v>
+        <v>4.8461</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1004</v>
+        <v>0.9214</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2944</v>
+        <v>3.9247</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9944</v>
+        <v>-1.4907</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4655</v>
+        <v>-0.6443</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.529</v>
+        <v>-0.8464</v>
       </c>
       <c r="P3" t="n">
         <v>-0.232</v>
@@ -688,19 +688,19 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6443</v>
+        <v>-0.2144</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0499</v>
+        <v>-0.3457</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5944</v>
+        <v>0.1314</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5361</v>
+        <v>1.3558</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>1.3558</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. LEE</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2991</v>
+        <v>3.5074</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5406</v>
+        <v>2.9576</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7585</v>
+        <v>0.5498</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3554</v>
+        <v>2.4004</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2771</v>
+        <v>3.6349</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0783</v>
+        <v>-1.2345</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8461</v>
+        <v>4.3949</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9214</v>
+        <v>4.1004</v>
       </c>
       <c r="L4" t="n">
-        <v>3.9247</v>
+        <v>0.2944</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4907</v>
+        <v>-1.9944</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6443</v>
+        <v>-0.4655</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8464</v>
+        <v>-1.529</v>
       </c>
       <c r="P4" t="n">
         <v>-0.232</v>
@@ -766,19 +766,19 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1801</v>
+        <v>0.8028</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1098</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0703</v>
+        <v>0.2247</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3558</v>
+        <v>0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3558</v>
+        <v>0.5361</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0001</v>
+        <v>2.2093</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1823</v>
+        <v>2.2569</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1821</v>
+        <v>-0.0477</v>
       </c>
       <c r="G5" t="n">
         <v>0.6860000000000001</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3664</v>
+        <v>-0.1573</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2592</v>
+        <v>-0.1845</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1072</v>
+        <v>0.0272</v>
       </c>
       <c r="V5" t="n">
         <v>2.1444</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SMITS</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6097</v>
+        <v>1.5005</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2022</v>
+        <v>0.5174</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4074</v>
+        <v>0.9831</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8678</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0384</v>
+        <v>0.168</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1706</v>
+        <v>-0.2309</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5756</v>
+        <v>2.0818</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4284</v>
+        <v>0.8339</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1472</v>
+        <v>1.2479</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7078</v>
+        <v>-2.1446</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.39</v>
+        <v>-0.6659</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3178</v>
+        <v>-1.4787</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>3.0154</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3501</v>
+        <v>0.0815</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3734</v>
+        <v>-0.1727</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7235</v>
+        <v>0.2541</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MUTAF</t>
+          <t>R. SMITS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.861</v>
+        <v>1.4924</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1535</v>
+        <v>1.3202</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2925</v>
+        <v>0.1722</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1531</v>
+        <v>0.8678</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1861</v>
+        <v>1.0384</v>
       </c>
       <c r="I7" t="n">
-        <v>0.967</v>
+        <v>-0.1706</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2282</v>
+        <v>1.5756</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0504</v>
+        <v>1.4284</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1778</v>
+        <v>0.1472</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0751</v>
+        <v>-0.7078</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1357</v>
+        <v>-0.39</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2108</v>
+        <v>-0.3178</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2921</v>
+        <v>0.2328</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0747</v>
+        <v>-0.2555</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2175</v>
+        <v>0.4883</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>D. MUTAF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8203</v>
+        <v>0.8946</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2068</v>
+        <v>1.1535</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6135</v>
+        <v>-0.2589</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.06279999999999999</v>
+        <v>1.1531</v>
       </c>
       <c r="H8" t="n">
-        <v>0.168</v>
+        <v>0.1861</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2309</v>
+        <v>0.967</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0818</v>
+        <v>1.2282</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8339</v>
+        <v>0.0504</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2479</v>
+        <v>1.1778</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1446</v>
+        <v>-0.0751</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6659</v>
+        <v>0.1357</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4787</v>
+        <v>-0.2108</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.0154</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5988</v>
+        <v>-0.2585</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4832</v>
+        <v>-0.0747</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1155</v>
+        <v>-0.1838</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.7484</v>
       </c>
       <c r="E9" t="n">
-        <v>0.603</v>
+        <v>0.7209</v>
       </c>
       <c r="F9" t="n">
         <v>0.0275</v>
@@ -1156,10 +1156,10 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1652</v>
+        <v>-0.0472</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6721</v>
+        <v>-0.5542</v>
       </c>
       <c r="U9" t="n">
         <v>0.507</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8086</v>
+        <v>-0.5898</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3656</v>
+        <v>-0.2476</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.443</v>
+        <v>-0.3422</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3527</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3141</v>
+        <v>-0.0953</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0901</v>
+        <v>0.0108</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5236</v>
+        <v>-2.499</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9379</v>
+        <v>-2.7452</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4142</v>
+        <v>0.2462</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0943</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3598</v>
+        <v>-0.3352</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9709</v>
+        <v>-0.7782</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6111</v>
+        <v>0.443</v>
       </c>
       <c r="V11" t="n">
         <v>0.3943</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4096</v>
+        <v>-3.4091</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4454</v>
+        <v>-2.7809</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9643</v>
+        <v>-0.6282</v>
       </c>
       <c r="G12" t="n">
         <v>0.6186</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0851</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5228</v>
+        <v>0.1417</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5623</v>
+        <v>-0.2262</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.1494</v>
+        <v>14.5229</v>
       </c>
       <c r="E13" t="n">
-        <v>12.7353</v>
+        <v>13.1088</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4139</v>
+        <v>1.414</v>
       </c>
       <c r="G13" t="n">
         <v>7.8114</v>
@@ -1456,7 +1456,7 @@
         <v>-6.065799999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.661199999999999</v>
+        <v>-7.661200000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-1.1599</v>
@@ -1468,13 +1468,13 @@
         <v>15.0769</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1186999999999997</v>
+        <v>0.2547000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.9637</v>
+        <v>-1.5904</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8451</v>
+        <v>1.8452</v>
       </c>
       <c r="V13" t="n">
         <v>7.6161</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.217</v>
+        <v>5.5257</v>
       </c>
       <c r="E14" t="n">
-        <v>7.6759</v>
+        <v>6.8502</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4589</v>
+        <v>-1.3245</v>
       </c>
       <c r="G14" t="n">
         <v>3.7784</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>0.601</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.767</v>
+        <v>-0.0587</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1661</v>
+        <v>-0.0316</v>
       </c>
       <c r="V14" t="n">
         <v>0.6778999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.769</v>
+        <v>1.1057</v>
       </c>
       <c r="E15" t="n">
-        <v>2.869</v>
+        <v>3.1049</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1</v>
+        <v>-1.9992</v>
       </c>
       <c r="G15" t="n">
         <v>0.9208</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4714</v>
+        <v>-0.1346</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5149</v>
+        <v>-0.279</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0435</v>
+        <v>0.1443</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2661</v>
+        <v>0.5692</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5885</v>
+        <v>0.8244</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3224</v>
+        <v>-0.2552</v>
       </c>
       <c r="G16" t="n">
         <v>0.8345</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5685</v>
+        <v>-0.2653</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1202</v>
+        <v>-0.8843</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5518</v>
+        <v>0.619</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2947</v>
+        <v>-0.4707</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.06610000000000001</v>
+        <v>0.5586</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2287</v>
+        <v>-1.0293</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5854</v>
+        <v>-0.8814</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9832</v>
+        <v>0.4972</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6022</v>
+        <v>-1.3786</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2696</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3929</v>
+        <v>1.4452</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6625</v>
+        <v>-0.482</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8551</v>
+        <v>-1.8447</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5904</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2647</v>
+        <v>-0.8966</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>2.935</v>
+        <v>-0.2309</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3239</v>
+        <v>-0.4046</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6111</v>
+        <v>0.1737</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2525</v>
+        <v>-1.214</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.212</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1491</v>
+        <v>-0.1352</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0629</v>
+        <v>-0.5538</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8814</v>
+        <v>-0.8015</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4972</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3786</v>
+        <v>-0.8097</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.757</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4452</v>
+        <v>0.8808</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.482</v>
+        <v>-0.1239</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8447</v>
+        <v>-1.5584</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.8726</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8966</v>
+        <v>-0.6859</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9722</v>
+        <v>0.3264</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1123</v>
+        <v>0.2675</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1401</v>
+        <v>0.0589</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.214</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.214</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3968</v>
+        <v>-2.232</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.843</v>
+        <v>-1.8353</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5538</v>
+        <v>-0.3967</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8015</v>
+        <v>-1.5854</v>
       </c>
       <c r="H19" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.9832</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8097</v>
+        <v>-0.6022</v>
       </c>
       <c r="J19" t="n">
-        <v>0.757</v>
+        <v>0.2696</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8808</v>
+        <v>-0.3929</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1239</v>
+        <v>0.6625</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5584</v>
+        <v>-1.8551</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8726</v>
+        <v>-0.5904</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6859</v>
+        <v>-1.2647</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3813</v>
+        <v>0.9976</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4402</v>
+        <v>0.5546</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0589</v>
+        <v>0.443</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.2525</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8465</v>
+        <v>-2.8103</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2639</v>
+        <v>-2.0298</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5826</v>
+        <v>-0.7805</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7147</v>
+        <v>-1.2801</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0013</v>
+        <v>0.6471</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.716</v>
+        <v>-1.9273</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7914</v>
+        <v>0.5214</v>
       </c>
       <c r="K20" t="n">
-        <v>1.768</v>
+        <v>1.3948</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0234</v>
+        <v>-0.8734</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5061</v>
+        <v>-1.8016</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7667</v>
+        <v>-0.7477</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.0539</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3528</v>
+        <v>-0.226</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0193</v>
+        <v>-0.2317</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3721</v>
+        <v>0.0057</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3247</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3329</v>
+        <v>-3.0488</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6196</v>
+        <v>-0.4998</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7133</v>
+        <v>-2.549</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2801</v>
+        <v>-0.7147</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6471</v>
+        <v>0.0013</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.9273</v>
+        <v>-0.716</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5214</v>
+        <v>1.7914</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3948</v>
+        <v>1.768</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8734</v>
+        <v>0.0234</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8016</v>
+        <v>-2.5061</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7477</v>
+        <v>-1.7667</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0539</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7486</v>
+        <v>0.1505</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8215</v>
+        <v>-0.2552</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.4057</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>-1.3247</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>J. MONTERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9668</v>
+        <v>-3.6132</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7191</v>
+        <v>-2.363</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2477</v>
+        <v>-1.2502</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.8105</v>
+        <v>-2.5701</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4453</v>
+        <v>-3.4466</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3652</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2868</v>
+        <v>-0.9362</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2366</v>
+        <v>-2.184</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0502</v>
+        <v>1.2479</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5236</v>
+        <v>-1.6339</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2087</v>
+        <v>-1.2626</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3149</v>
+        <v>-0.3713</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5395</v>
+        <v>-0.5946</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7275</v>
+        <v>-0.2671</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.188</v>
+        <v>-0.3275</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1658</v>
+        <v>-4.0307</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0517</v>
+        <v>-3.8158</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1141</v>
+        <v>-0.2149</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7015</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0004</v>
+        <v>0.1346</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8962</v>
+        <v>-0.6603</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. MONTERO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1858</v>
+        <v>-4.4551</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8348</v>
+        <v>-2.073</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.351</v>
+        <v>-2.3822</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5701</v>
+        <v>-3.8105</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.4466</v>
+        <v>-2.4453</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8764999999999999</v>
+        <v>-1.3652</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9362</v>
+        <v>-1.2868</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.184</v>
+        <v>-1.2366</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2479</v>
+        <v>-0.0502</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.6339</v>
+        <v>-2.5236</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2626</v>
+        <v>-1.2087</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3713</v>
+        <v>-1.3149</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q24" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1672</v>
+        <v>0.0512</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7389</v>
+        <v>0.3736</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4283</v>
+        <v>-0.3224</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2362,16 +2362,16 @@
         <v>-14.1492</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.413900000000001</v>
+        <v>-1.413799999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.7354</v>
+        <v>-12.7355</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.8115</v>
+        <v>-7.811500000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.5064</v>
+        <v>-6.506399999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-1.305199999999999</v>
@@ -2404,10 +2404,10 @@
         <v>16.2368</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1187000000000002</v>
+        <v>0.1186</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.8451</v>
+        <v>-1.8452</v>
       </c>
       <c r="U25" t="n">
         <v>1.9637</v>
@@ -2419,7 +2419,7 @@
         <v>1.7812</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.3973</v>
+        <v>-9.397300000000001</v>
       </c>
     </row>
   </sheetData>
